--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Laptop\e\VVSS\CamiVVSS_ro2025-2026\Labs\CheckListsAll\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\Facultate\VVSS\docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE83867-3721-469D-B0A3-67FDA22FF09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D69D8F9F-0006-455A-A4AE-EC998CD3C0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="650" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="72">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -135,13 +135,135 @@
   </si>
   <si>
     <t>Effort to perform tool-based code analysis (hours):</t>
+  </si>
+  <si>
+    <t>Secure George-Sebastian</t>
+  </si>
+  <si>
+    <t>Stanca Vlad Tudor</t>
+  </si>
+  <si>
+    <t>C01</t>
+  </si>
+  <si>
+    <t>C04</t>
+  </si>
+  <si>
+    <t>C06</t>
+  </si>
+  <si>
+    <t>C07</t>
+  </si>
+  <si>
+    <t>C08</t>
+  </si>
+  <si>
+    <t>C09</t>
+  </si>
+  <si>
+    <t>Prelucrarea datelor trebuie făcută în service/repository, nu în controller</t>
+  </si>
+  <si>
+    <t>DrinkShopApp 21-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DrinkShopApp </t>
+  </si>
+  <si>
+    <t>Nu se gestionează erorile - "throws Exception"</t>
+  </si>
+  <si>
+    <t>Prelucrările (filtrările) ar trebui realizare în repository</t>
+  </si>
+  <si>
+    <t>ProductService 45, 52</t>
+  </si>
+  <si>
+    <t>La update se inserează toți parametri obiectului în loc de o instanța lui (=&gt; updateProduct(prod) )</t>
+  </si>
+  <si>
+    <t>Toate Service-urile</t>
+  </si>
+  <si>
+    <t>La metodele de Add și Update nu sunt apelați validatorii</t>
+  </si>
+  <si>
+    <t>ProductService 21
+DrinkShopService 38</t>
+  </si>
+  <si>
+    <t>DrinkShopService 23</t>
+  </si>
+  <si>
+    <t>Repository&lt;Integer,Stoc&gt; stocService =&gt; stocRepo</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>RetetaValidator 14</t>
+  </si>
+  <si>
+    <t>Tipul declarat este double, însă se pune ca parametru int</t>
+  </si>
+  <si>
+    <t>FileStocRepository 24-27
+Stoc 10</t>
+  </si>
+  <si>
+    <t>.get(0) poate arunca IndexOutOfBoundsException</t>
+  </si>
+  <si>
+    <t>ReceiptGenerator
+CsvExporter</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>Repository-uri</t>
+  </si>
+  <si>
+    <t>Service-uri/Repository-uri</t>
+  </si>
+  <si>
+    <t>Nu se verifică dacă operațiile din fișiere se execută corect - nu se gestionează erorile IO. Nu se verifică existența duplicatelor</t>
+  </si>
+  <si>
+    <t>DrinkShopController</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Există metoda ShowError pentru erori, dar nu există și pentru warnings, infos - cod duplicat </t>
+  </si>
+  <si>
+    <t>OrderService 43
+DrinkShopController 123</t>
+  </si>
+  <si>
+    <t>Metodă ineficientă - există deja implementare a metodei utilizate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OrderService 43
+</t>
+  </si>
+  <si>
+    <t>Nu se verifică dacă repository-urile sunt create corect. Problemă ce apare din cauza căilor relative ale fișierelor -</t>
+  </si>
+  <si>
+    <t>Nu se verifică dacă datele de intrare sunt valide în metoda extractEntity</t>
+  </si>
+  <si>
+    <t>De ce se folosește AtomicReference și nu String/StringBuilder?</t>
+  </si>
+  <si>
+    <t>Metodă ineficientă. Poți lua Product din OrderItem și nu prin stream</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,6 +346,15 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -326,7 +457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -398,6 +529,31 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -707,19 +863,19 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.26953125" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.26953125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.453125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.90625" style="6"/>
+    <col min="1" max="1" width="8.85546875" style="6"/>
+    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
+    <col min="3" max="4" width="16.28515625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
+    <col min="6" max="8" width="8.85546875" style="6"/>
     <col min="9" max="9" width="21" style="6" customWidth="1"/>
-    <col min="10" max="10" width="14.453125" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="8.90625" style="6"/>
+    <col min="10" max="10" width="14.42578125" style="6" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
@@ -730,7 +886,7 @@
       <c r="I1" s="23"/>
       <c r="J1" s="23"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B2" s="24" t="s">
         <v>19</v>
       </c>
@@ -745,14 +901,14 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H3" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
@@ -766,7 +922,7 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
@@ -780,7 +936,7 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
@@ -788,14 +944,14 @@
       <c r="D6" s="22"/>
       <c r="E6" s="22"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="22"/>
       <c r="E7" s="22"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -809,7 +965,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <v>1</v>
       </c>
@@ -817,7 +973,7 @@
       <c r="D10" s="1"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
@@ -826,7 +982,7 @@
       <c r="D11" s="1"/>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B25" si="0">B11+1</f>
         <v>3</v>
@@ -835,7 +991,7 @@
       <c r="D12" s="1"/>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -844,7 +1000,7 @@
       <c r="D13" s="1"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -853,7 +1009,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -862,7 +1018,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -871,7 +1027,7 @@
       <c r="D16" s="1"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -880,7 +1036,7 @@
       <c r="D17" s="1"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -889,7 +1045,7 @@
       <c r="D18" s="3"/>
       <c r="E18" s="15"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -898,7 +1054,7 @@
       <c r="D19" s="3"/>
       <c r="E19" s="15"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -907,7 +1063,7 @@
       <c r="D20" s="3"/>
       <c r="E20" s="15"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -916,7 +1072,7 @@
       <c r="D21" s="3"/>
       <c r="E21" s="15"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -925,7 +1081,7 @@
       <c r="D22" s="3"/>
       <c r="E22" s="15"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -934,7 +1090,7 @@
       <c r="D23" s="3"/>
       <c r="E23" s="15"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -943,7 +1099,7 @@
       <c r="D24" s="3"/>
       <c r="E24" s="15"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -952,7 +1108,7 @@
       <c r="D25" s="3"/>
       <c r="E25" s="15"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="11" t="s">
         <v>8</v>
       </c>
@@ -979,18 +1135,18 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.26953125" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.26953125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.453125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.90625" style="6"/>
-    <col min="9" max="9" width="22.08984375" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="6"/>
+    <col min="1" max="1" width="8.85546875" style="6"/>
+    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
+    <col min="3" max="4" width="16.28515625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
+    <col min="6" max="8" width="8.85546875" style="6"/>
+    <col min="9" max="9" width="22.140625" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
@@ -1001,7 +1157,7 @@
       <c r="I1" s="23"/>
       <c r="J1" s="23"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B2" s="24" t="s">
         <v>18</v>
       </c>
@@ -1016,14 +1172,14 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H3" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
@@ -1037,7 +1193,7 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
@@ -1051,7 +1207,7 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
@@ -1059,14 +1215,14 @@
       <c r="D6" s="22"/>
       <c r="E6" s="22"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="22"/>
       <c r="E7" s="22"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1080,7 +1236,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <v>1</v>
       </c>
@@ -1088,7 +1244,7 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
@@ -1097,7 +1253,7 @@
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B26" si="0">B11+1</f>
         <v>3</v>
@@ -1106,7 +1262,7 @@
       <c r="D12" s="1"/>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1115,7 +1271,7 @@
       <c r="D13" s="1"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1124,7 +1280,7 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1133,7 +1289,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1142,7 +1298,7 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1151,7 +1307,7 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1160,7 +1316,7 @@
       <c r="D18" s="1"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1169,7 +1325,7 @@
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1178,7 +1334,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1187,7 +1343,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1196,7 +1352,7 @@
       <c r="D22" s="1"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1205,7 +1361,7 @@
       <c r="D23" s="1"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1214,7 +1370,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1223,7 +1379,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1232,7 +1388,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C28" s="11" t="s">
         <v>8</v>
       </c>
@@ -1258,20 +1414,21 @@
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.26953125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.26953125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.453125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.90625" style="6"/>
-    <col min="9" max="9" width="26.7265625" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="6"/>
+    <col min="1" max="1" width="8.85546875" style="6"/>
+    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="51.7109375" style="6" customWidth="1"/>
+    <col min="6" max="7" width="8.85546875" style="6"/>
+    <col min="8" max="8" width="11.140625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="26.7109375" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
@@ -1282,7 +1439,7 @@
       <c r="I1" s="23"/>
       <c r="J1" s="23"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B2" s="24" t="s">
         <v>17</v>
       </c>
@@ -1297,14 +1454,18 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I3" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="37">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
@@ -1315,10 +1476,14 @@
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I4" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="37">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
@@ -1332,22 +1497,26 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22"/>
+      <c r="D6" s="22" t="s">
+        <v>33</v>
+      </c>
       <c r="E6" s="22"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="22"/>
+      <c r="D7" s="36">
+        <v>46091</v>
+      </c>
       <c r="E7" s="22"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1361,200 +1530,280 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="3">
+    <row r="10" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="44">
         <v>1</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B11" s="3">
-        <f>B10+1</f>
+      <c r="C10" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="B11" s="44">
+        <f t="shared" ref="B11:B24" si="0">B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B12" s="3">
-        <f t="shared" ref="B12:B30" si="0">B11+1</f>
+      <c r="C11" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="B12" s="44">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B13" s="3">
+      <c r="C12" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="42" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="B13" s="44">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B14" s="3">
+      <c r="C13" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="B14" s="44">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B15" s="3">
+      <c r="C14" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="B15" s="44">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="3">
+      <c r="C15" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="B16" s="44">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B17" s="3">
+      <c r="C16" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="44">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B18" s="3">
+      <c r="C17" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B18" s="44">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B19" s="3">
+      <c r="C18" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="43" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B19" s="44">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B20" s="3">
+      <c r="C19" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" s="43" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B20" s="44">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B21" s="3">
+      <c r="C20" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="43" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="44">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B22" s="3">
+      <c r="C21" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="43" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B22" s="44">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B23" s="3">
+      <c r="C22" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="43" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="44">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B24" s="3">
+      <c r="C23" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="43" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B24" s="44">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B25" s="3">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B26" s="3">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B27" s="3">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="1"/>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B28" s="3">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="C28" s="1"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B29" s="3">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B30" s="3">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="C32" s="11" t="s">
+      <c r="C24" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" s="43" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="3"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="43"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="3"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="43"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="3"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="43"/>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="3"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="43"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="3"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="43"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30" s="3"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="43"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="3"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="43"/>
+    </row>
+    <row r="33" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C33" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D32" s="12"/>
-      <c r="E32" s="1"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="1">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1576,20 +1825,20 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.26953125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.26953125" style="6" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" style="6"/>
+    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" style="6" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="23.90625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.6328125" style="6" customWidth="1"/>
-    <col min="7" max="8" width="8.90625" style="6"/>
-    <col min="9" max="9" width="26.7265625" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="6"/>
+    <col min="5" max="5" width="23.85546875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" style="6" customWidth="1"/>
+    <col min="7" max="8" width="8.85546875" style="6"/>
+    <col min="9" max="9" width="26.7109375" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
@@ -1600,7 +1849,7 @@
       <c r="I1" s="23"/>
       <c r="J1" s="23"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B2" s="24" t="s">
         <v>31</v>
       </c>
@@ -1615,14 +1864,14 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H3" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C4" s="16" t="s">
         <v>25</v>
       </c>
@@ -1634,7 +1883,7 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
@@ -1646,7 +1895,7 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>1</v>
@@ -1655,7 +1904,7 @@
       <c r="E6" s="22"/>
       <c r="F6" s="20"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1672,7 +1921,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <v>1</v>
       </c>
@@ -1681,7 +1930,7 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
@@ -1691,7 +1940,7 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
@@ -1701,7 +1950,7 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1711,7 +1960,7 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1721,7 +1970,7 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1731,7 +1980,7 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1741,7 +1990,7 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1751,7 +2000,7 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1761,7 +2010,7 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1771,7 +2020,7 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1781,7 +2030,7 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1791,7 +2040,7 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1801,7 +2050,7 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1811,7 +2060,7 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1821,7 +2070,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1831,7 +2080,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1841,7 +2090,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1851,7 +2100,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1861,7 +2110,7 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1871,7 +2120,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1881,7 +2130,7 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C32" s="34" t="s">
         <v>32</v>
       </c>
@@ -1889,7 +2138,7 @@
       <c r="E32" s="35"/>
       <c r="F32" s="18"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F35" s="21"/>
     </row>
   </sheetData>

--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\Facultate\VVSS\docs\Lab01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Informatica\vvss\docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D69D8F9F-0006-455A-A4AE-EC998CD3C0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB49BF7-55C4-4CF1-9C70-7E0952C11976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="650" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="83">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -257,6 +255,39 @@
   </si>
   <si>
     <t>Metodă ineficientă. Poți lua Product din OrderItem și nu prin stream</t>
+  </si>
+  <si>
+    <t>R01</t>
+  </si>
+  <si>
+    <t>R02</t>
+  </si>
+  <si>
+    <t>R06</t>
+  </si>
+  <si>
+    <t>R07</t>
+  </si>
+  <si>
+    <t>Cerinte functionale</t>
+  </si>
+  <si>
+    <t>Nu este specificat ce este un "tip" si ce este o "categorie" pentru fiecare bautura. Cum va fi reprezentat in cod? Enum? String?</t>
+  </si>
+  <si>
+    <t>Nu este mentionat nicaieri pretul unui produs, cum este setat, ce tip are</t>
+  </si>
+  <si>
+    <t>Nu este specificat nicaieri cat de mare trebuie sa fie aceasta aplicatie, cati utilizatori trebuie sa suporte simultan</t>
+  </si>
+  <si>
+    <t>Nu este specificat modalitatea de reprezentare a datelor in fisier. Trebuie sa fie citibile de care un om sau ajunge sa fie intelese doar de catre masina?</t>
+  </si>
+  <si>
+    <t>30 min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La finalul unei zile nu este specificat cum se salveaza </t>
   </si>
 </sst>
 </file>
@@ -489,14 +520,47 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -515,46 +579,13 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="16" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -867,7 +898,8 @@
   <cols>
     <col min="1" max="1" width="8.85546875" style="6"/>
     <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.28515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
     <col min="6" max="8" width="8.85546875" style="6"/>
     <col min="9" max="9" width="21" style="6" customWidth="1"/>
@@ -880,19 +912,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -905,31 +937,39 @@
       <c r="H3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
+      <c r="I3" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="9">
+        <v>236</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="25"/>
+      <c r="E4" s="36"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="I4" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="9">
+        <v>236</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="27"/>
+      <c r="E5" s="38"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -941,15 +981,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
+      <c r="D6" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="30"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
+      <c r="D7" s="29">
+        <v>46091</v>
+      </c>
+      <c r="E7" s="30"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
@@ -965,49 +1009,71 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <v>1</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E11" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B25" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E12" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
+      <c r="C13" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="D13" s="1"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E13" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="D14" s="1"/>
-      <c r="E14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
@@ -1113,7 +1179,9 @@
         <v>8</v>
       </c>
       <c r="D27" s="12"/>
-      <c r="E27" s="1"/>
+      <c r="E27" s="44" t="s">
+        <v>81</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1151,19 +1219,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1176,31 +1244,39 @@
       <c r="H3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
+      <c r="I3" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="9">
+        <v>236</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="28"/>
+      <c r="E4" s="39"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="I4" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="9">
+        <v>236</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="30"/>
+      <c r="E5" s="41"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1212,15 +1288,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
+      <c r="D6" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="30"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
+      <c r="D7" s="29">
+        <v>46091</v>
+      </c>
+      <c r="E7" s="30"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
@@ -1433,19 +1513,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1458,10 +1538,10 @@
       <c r="H3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="38" t="s">
+      <c r="I3" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="37">
+      <c r="J3" s="9">
         <v>236</v>
       </c>
     </row>
@@ -1469,17 +1549,17 @@
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="31"/>
+      <c r="E4" s="32"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="39" t="s">
+      <c r="I4" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="37">
+      <c r="J4" s="9">
         <v>236</v>
       </c>
     </row>
@@ -1487,10 +1567,10 @@
       <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="33"/>
+      <c r="E5" s="35"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1502,19 +1582,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="30"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="36">
+      <c r="D7" s="29">
         <v>46091</v>
       </c>
-      <c r="E7" s="22"/>
+      <c r="E7" s="30"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
@@ -1531,270 +1611,270 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="44">
+      <c r="B10" s="28">
         <v>1</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="41" t="s">
+      <c r="D10" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="27" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="B11" s="44">
+      <c r="B11" s="28">
         <f t="shared" ref="B11:B24" si="0">B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="41" t="s">
+      <c r="D11" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="42" t="s">
+      <c r="E11" s="26" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B12" s="44">
+      <c r="B12" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="41" t="s">
+      <c r="D12" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="42" t="s">
+      <c r="E12" s="26" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B13" s="44">
+      <c r="B13" s="28">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="40" t="s">
+      <c r="D13" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="43" t="s">
+      <c r="E13" s="27" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B14" s="44">
+      <c r="B14" s="28">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="41" t="s">
+      <c r="D14" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="43" t="s">
+      <c r="E14" s="27" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B15" s="44">
+      <c r="B15" s="28">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="41" t="s">
+      <c r="D15" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="43" t="s">
+      <c r="E15" s="27" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B16" s="44">
+      <c r="B16" s="28">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="41" t="s">
+      <c r="D16" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="43" t="s">
+      <c r="E16" s="27" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="44">
+      <c r="B17" s="28">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="41" t="s">
+      <c r="D17" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="43" t="s">
+      <c r="E17" s="27" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B18" s="44">
+      <c r="B18" s="28">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="40" t="s">
+      <c r="D18" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="E18" s="43" t="s">
+      <c r="E18" s="27" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B19" s="44">
+      <c r="B19" s="28">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="40" t="s">
+      <c r="C19" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="41" t="s">
+      <c r="D19" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="E19" s="43" t="s">
+      <c r="E19" s="27" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="B20" s="44">
+      <c r="B20" s="28">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="40" t="s">
+      <c r="C20" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="41" t="s">
+      <c r="D20" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="E20" s="43" t="s">
+      <c r="E20" s="27" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="44">
+      <c r="B21" s="28">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="40" t="s">
+      <c r="C21" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="40" t="s">
+      <c r="D21" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="43" t="s">
+      <c r="E21" s="27" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B22" s="44">
+      <c r="B22" s="28">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="41" t="s">
+      <c r="D22" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="43" t="s">
+      <c r="E22" s="27" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="44">
+      <c r="B23" s="28">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="40" t="s">
+      <c r="C23" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="41" t="s">
+      <c r="D23" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="43" t="s">
+      <c r="E23" s="27" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="B24" s="44">
+      <c r="B24" s="28">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="D24" s="41" t="s">
+      <c r="D24" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E24" s="43" t="s">
+      <c r="E24" s="27" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="3"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="43"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="27"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="3"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="43"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="27"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="3"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="43"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="27"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="3"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="43"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="27"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="3"/>
-      <c r="C29" s="40"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="43"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="27"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="3"/>
-      <c r="C30" s="40"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="43"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="27"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="3"/>
-      <c r="C31" s="40"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="43"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="27"/>
     </row>
     <row r="33" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C33" s="11" t="s">
@@ -1843,19 +1923,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1875,8 +1955,8 @@
       <c r="C4" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1887,8 +1967,8 @@
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1900,8 +1980,8 @@
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
       <c r="F6" s="20"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -2131,11 +2211,11 @@
       <c r="F30" s="2"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C32" s="34" t="s">
+      <c r="C32" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
       <c r="F32" s="18"/>
     </row>
     <row r="35" spans="6:6" x14ac:dyDescent="0.25">

--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Informatica\vvss\docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB49BF7-55C4-4CF1-9C70-7E0952C11976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C91FCB-176C-4B1B-AA39-2209B260BE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -287,7 +287,7 @@
     <t>30 min</t>
   </si>
   <si>
-    <t xml:space="preserve">La finalul unei zile nu este specificat cum se salveaza </t>
+    <t>La finalul unei zile nu este specificat modul de salvare a informatiilor despre comenzile inregistrate: manual sau automat</t>
   </si>
 </sst>
 </file>
@@ -540,6 +540,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="16" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -549,43 +550,42 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="16" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -912,11 +912,11 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B2" s="33" t="s">
@@ -948,10 +948,10 @@
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="36"/>
+      <c r="E4" s="34"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -966,10 +966,10 @@
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="38"/>
+      <c r="E5" s="36"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -981,19 +981,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="30"/>
+      <c r="E6" s="31"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>46091</v>
       </c>
-      <c r="E7" s="30"/>
+      <c r="E7" s="31"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
@@ -1062,7 +1062,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1179,7 +1179,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="12"/>
-      <c r="E27" s="44" t="s">
+      <c r="E27" s="29" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1219,11 +1219,11 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B2" s="33" t="s">
@@ -1255,10 +1255,10 @@
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="39"/>
+      <c r="E4" s="37"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1273,10 +1273,10 @@
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="41"/>
+      <c r="E5" s="39"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1288,19 +1288,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="30"/>
+      <c r="E6" s="31"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>46091</v>
       </c>
-      <c r="E7" s="30"/>
+      <c r="E7" s="31"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
@@ -1513,11 +1513,11 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B2" s="33" t="s">
@@ -1549,10 +1549,10 @@
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="32"/>
+      <c r="E4" s="40"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1567,10 +1567,10 @@
       <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="35"/>
+      <c r="E5" s="42"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1582,19 +1582,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="30"/>
+      <c r="E6" s="31"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>46091</v>
       </c>
-      <c r="E7" s="30"/>
+      <c r="E7" s="31"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
@@ -1923,11 +1923,11 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B2" s="33" t="s">
@@ -1955,8 +1955,8 @@
       <c r="C4" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1967,8 +1967,8 @@
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1980,8 +1980,8 @@
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
       <c r="F6" s="20"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -2211,11 +2211,11 @@
       <c r="F30" s="2"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C32" s="42" t="s">
+      <c r="C32" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
       <c r="F32" s="18"/>
     </row>
     <row r="35" spans="6:6" x14ac:dyDescent="0.25">

--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Informatica\vvss\docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C91FCB-176C-4B1B-AA39-2209B260BE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5787AE9A-AC2E-4E64-BA4E-671A252658C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -288,6 +288,33 @@
   </si>
   <si>
     <t>La finalul unei zile nu este specificat modul de salvare a informatiilor despre comenzile inregistrate: manual sau automat</t>
+  </si>
+  <si>
+    <t>A01</t>
+  </si>
+  <si>
+    <t>A03</t>
+  </si>
+  <si>
+    <t>A05</t>
+  </si>
+  <si>
+    <t>Requirements_MyDrinkShop.ong</t>
+  </si>
+  <si>
+    <t>DrinkShopService primeste in constructor repository-uri, cand el ar trebui sa primeasca service-urile create din exterior, conform Dependency Injection</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>Nu exista nicio legatura intre reteta si produse, o reteta ar trebui sa tina de / sa depinda de un produs existent</t>
+  </si>
+  <si>
+    <t>Nu este clar din diagrama care este legatura validatorilor cu restul claselor din proiect</t>
+  </si>
+  <si>
+    <t>Nu este deloc clar, lipseste implementarea functionalitatii 3, cea de adaugare, modificare si stergere a tipului si categoriei de bautura</t>
   </si>
 </sst>
 </file>
@@ -1207,7 +1234,8 @@
   <cols>
     <col min="1" max="1" width="8.85546875" style="6"/>
     <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.28515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
     <col min="6" max="8" width="8.85546875" style="6"/>
     <col min="9" max="9" width="22.140625" style="6" customWidth="1"/>
@@ -1316,40 +1344,58 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <v>1</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E11" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B26" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E12" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
+      <c r="C13" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="D13" s="1"/>
-      <c r="E13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
@@ -1473,7 +1519,9 @@
         <v>8</v>
       </c>
       <c r="D28" s="12"/>
-      <c r="E28" s="1"/>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5787AE9A-AC2E-4E64-BA4E-671A252658C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="650" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>

--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Informatica\vvss\docs\Lab01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\Facultate\VVSS\docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5787AE9A-AC2E-4E64-BA4E-671A252658C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7D790E4-A94E-418E-A709-49B0F3858C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="650" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="650" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="122">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -315,13 +315,114 @@
   </si>
   <si>
     <t>Nu este deloc clar, lipseste implementarea functionalitatii 3, cea de adaugare, modificare si stergere a tipului si categoriei de bautura</t>
+  </si>
+  <si>
+    <t>SonarQube</t>
+  </si>
+  <si>
+    <t>CsvExporter 14</t>
+  </si>
+  <si>
+    <t>"Add a private constructor to hide the implicit public one"</t>
+  </si>
+  <si>
+    <t>CsvExporter 20</t>
+  </si>
+  <si>
+    <t>class CsvExporter { // Noncompliant
+…
+}</t>
+  </si>
+  <si>
+    <t>class CsvExporter { // Compliant
+  private CsvExporter() {
+    /* This utility class should not be instantiated */
+  }</t>
+  </si>
+  <si>
+    <t>public static void exportOrders(List&lt;Product&gt; products, List&lt;Order&gt; orders, String path)</t>
+  </si>
+  <si>
+    <t>public static void exportOrders(List&lt;Order&gt; orders, String path)</t>
+  </si>
+  <si>
+    <t>CsvExporter 39</t>
+  </si>
+  <si>
+    <t>catch (IOException e) {
+            throw new RuntimeException(e);
+        }</t>
+  </si>
+  <si>
+    <t>catch (IOException e) {
+            throw new CsvExportException(e);
+        }</t>
+  </si>
+  <si>
+    <t>FileAbstractRepository 12</t>
+  </si>
+  <si>
+    <t>public FileAbstractRepository(String fileName)</t>
+  </si>
+  <si>
+    <t>protected FileAbstractRepository(String fileName)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> //loadFromFile();</t>
+  </si>
+  <si>
+    <t>FileAbstractRepository 14</t>
+  </si>
+  <si>
+    <t>FileAbstractRepository 7</t>
+  </si>
+  <si>
+    <t>"Unused method parameters should be removed"</t>
+  </si>
+  <si>
+    <t>"Generic exceptions should never be thrown"</t>
+  </si>
+  <si>
+    <t>"Constructors of an "abstract" class should not be declared "public""</t>
+  </si>
+  <si>
+    <t>"Sections of code should not be commented out"</t>
+  </si>
+  <si>
+    <t>"Type parameter names should comply with a naming convention"</t>
+  </si>
+  <si>
+    <t>"ID" este mai ușor de înțeles, decât doar "I"</t>
+  </si>
+  <si>
+    <t>"Lambdas containing only one statement should not nest this statement in a block"</t>
+  </si>
+  <si>
+    <t>RetetaValidator 27-29</t>
+  </si>
+  <si>
+    <t>.forEach(entry -&gt; {          errors.append("[").append(entry.getDenumire()).append("]").append("cantitate negativa sau zero").append("\n");
+                });</t>
+  </si>
+  <si>
+    <t>.forEach(entry -&gt;
+errors.append("[").append(entry.getDenumire()).append("]").append("cantitate negativa sau zero").append("\n"));</t>
+  </si>
+  <si>
+    <t>"Unused "private" fields should be removed"</t>
+  </si>
+  <si>
+    <t>OrderService 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    private final Repository&lt;Integer, Product&gt; productRepo;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -414,6 +515,14 @@
       <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="5">
@@ -515,7 +624,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -568,17 +677,26 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -589,15 +707,6 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -612,6 +721,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -939,19 +1051,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -975,10 +1087,10 @@
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="34"/>
+      <c r="E4" s="37"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -993,10 +1105,10 @@
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="36"/>
+      <c r="E5" s="39"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1008,19 +1120,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="31"/>
+      <c r="E6" s="33"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="34">
         <v>46091</v>
       </c>
-      <c r="E7" s="31"/>
+      <c r="E7" s="33"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
@@ -1247,19 +1359,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1283,10 +1395,10 @@
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="37"/>
+      <c r="E4" s="32"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1301,10 +1413,10 @@
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="39"/>
+      <c r="E5" s="36"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1316,19 +1428,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="31"/>
+      <c r="E6" s="33"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="34">
         <v>46091</v>
       </c>
-      <c r="E7" s="31"/>
+      <c r="E7" s="33"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
@@ -1561,19 +1673,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1630,19 +1742,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="31"/>
+      <c r="E6" s="33"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="34">
         <v>46091</v>
       </c>
-      <c r="E7" s="31"/>
+      <c r="E7" s="33"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
@@ -1957,10 +2069,10 @@
   <cols>
     <col min="1" max="1" width="8.85546875" style="6"/>
     <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="23.85546875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="49" style="6" customWidth="1"/>
+    <col min="5" max="5" width="48.85546875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="52.140625" style="6" customWidth="1"/>
     <col min="7" max="8" width="8.85546875" style="6"/>
     <col min="9" max="9" width="26.7109375" style="6" customWidth="1"/>
     <col min="10" max="16384" width="8.85546875" style="6"/>
@@ -1971,19 +2083,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1996,27 +2108,39 @@
       <c r="H3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
+      <c r="I3" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="9">
+        <v>236</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C4" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="40"/>
+      <c r="D4" s="40" t="s">
+        <v>92</v>
+      </c>
       <c r="E4" s="40"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="I4" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="9">
+        <v>236</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
+      <c r="D5" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="33"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -2028,8 +2152,10 @@
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
+      <c r="D6" s="34">
+        <v>46092</v>
+      </c>
+      <c r="E6" s="33"/>
       <c r="F6" s="20"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -2049,174 +2175,232 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <v>1</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C10" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="F10" s="45" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C11" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="F11" s="45" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="36" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C12" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>101</v>
+      </c>
+      <c r="F12" s="45" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="C13" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="F13" s="45" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C14" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="F14" s="45"/>
+    </row>
+    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C15" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C16" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="F16" s="45" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="24" x14ac:dyDescent="0.25">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
+      <c r="C17" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" s="45" t="s">
+        <v>121</v>
+      </c>
+      <c r="F17" s="45"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="3">

--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\Facultate\VVSS\docs\Lab01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\geose\OneDrive\Desktop\Facultate\SEM_VI\VVSS\docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7D790E4-A94E-418E-A709-49B0F3858C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF6A869-0031-4A41-96CF-EE863629701E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="650" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="650" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="115">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -169,12 +169,6 @@
   </si>
   <si>
     <t>Nu se gestionează erorile - "throws Exception"</t>
-  </si>
-  <si>
-    <t>Prelucrările (filtrările) ar trebui realizare în repository</t>
-  </si>
-  <si>
-    <t>ProductService 45, 52</t>
   </si>
   <si>
     <t>La update se inserează toți parametri obiectului în loc de o instanța lui (=&gt; updateProduct(prod) )</t>
@@ -196,17 +190,7 @@
     <t>Repository&lt;Integer,Stoc&gt; stocService =&gt; stocRepo</t>
   </si>
   <si>
-    <t>C12</t>
-  </si>
-  <si>
     <t>RetetaValidator 14</t>
-  </si>
-  <si>
-    <t>Tipul declarat este double, însă se pune ca parametru int</t>
-  </si>
-  <si>
-    <t>FileStocRepository 24-27
-Stoc 10</t>
   </si>
   <si>
     <t>.get(0) poate arunca IndexOutOfBoundsException</t>
@@ -228,23 +212,9 @@
     <t>Nu se verifică dacă operațiile din fișiere se execută corect - nu se gestionează erorile IO. Nu se verifică existența duplicatelor</t>
   </si>
   <si>
-    <t>DrinkShopController</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Există metoda ShowError pentru erori, dar nu există și pentru warnings, infos - cod duplicat </t>
-  </si>
-  <si>
-    <t>OrderService 43
-DrinkShopController 123</t>
-  </si>
-  <si>
     <t>Metodă ineficientă - există deja implementare a metodei utilizate</t>
   </si>
   <si>
-    <t xml:space="preserve">OrderService 43
-</t>
-  </si>
-  <si>
     <t>Nu se verifică dacă repository-urile sunt create corect. Problemă ce apare din cauza căilor relative ale fișierelor -</t>
   </si>
   <si>
@@ -297,9 +267,6 @@
   </si>
   <si>
     <t>A05</t>
-  </si>
-  <si>
-    <t>Requirements_MyDrinkShop.ong</t>
   </si>
   <si>
     <t>DrinkShopService primeste in constructor repository-uri, cand el ar trebui sa primeasca service-urile create din exterior, conform Dependency Injection</t>
@@ -416,6 +383,15 @@
   </si>
   <si>
     <t xml:space="preserve">    private final Repository&lt;Integer, Product&gt; productRepo;</t>
+  </si>
+  <si>
+    <t>Requirements_MyDrinkShop.png</t>
+  </si>
+  <si>
+    <t>DrinkShopController 123</t>
+  </si>
+  <si>
+    <t>OrderService 43</t>
   </si>
 </sst>
 </file>
@@ -677,36 +653,39 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -721,9 +700,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1033,37 +1009,37 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="6"/>
-    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.85546875" style="6"/>
+    <col min="1" max="1" width="8.88671875" style="6"/>
+    <col min="2" max="2" width="12.33203125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.44140625" style="6" customWidth="1"/>
+    <col min="6" max="8" width="8.88671875" style="6"/>
     <col min="9" max="9" width="21" style="6" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="6"/>
+    <col min="10" max="10" width="14.44140625" style="6" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="31" t="s">
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1072,7 +1048,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H3" s="17" t="s">
         <v>20</v>
       </c>
@@ -1083,14 +1059,14 @@
         <v>236</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="37"/>
+      <c r="E4" s="35"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1101,40 +1077,40 @@
         <v>236</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="39"/>
+      <c r="E5" s="37"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="33"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E6" s="32"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="31">
         <v>46091</v>
       </c>
-      <c r="E7" s="33"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E7" s="32"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1148,73 +1124,73 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B25" si="0">B11+1</f>
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1223,7 +1199,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1232,7 +1208,7 @@
       <c r="D16" s="1"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1241,7 +1217,7 @@
       <c r="D17" s="1"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1250,7 +1226,7 @@
       <c r="D18" s="3"/>
       <c r="E18" s="15"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1259,7 +1235,7 @@
       <c r="D19" s="3"/>
       <c r="E19" s="15"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1268,7 +1244,7 @@
       <c r="D20" s="3"/>
       <c r="E20" s="15"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1277,7 +1253,7 @@
       <c r="D21" s="3"/>
       <c r="E21" s="15"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1286,7 +1262,7 @@
       <c r="D22" s="3"/>
       <c r="E22" s="15"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1295,7 +1271,7 @@
       <c r="D23" s="3"/>
       <c r="E23" s="15"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1304,7 +1280,7 @@
       <c r="D24" s="3"/>
       <c r="E24" s="15"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1313,13 +1289,13 @@
       <c r="D25" s="3"/>
       <c r="E25" s="15"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C27" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="29" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1342,36 +1318,36 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="6"/>
-    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.85546875" style="6"/>
-    <col min="9" max="9" width="22.140625" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="6"/>
+    <col min="1" max="1" width="8.88671875" style="6"/>
+    <col min="2" max="2" width="12.33203125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.44140625" style="6" customWidth="1"/>
+    <col min="6" max="8" width="8.88671875" style="6"/>
+    <col min="9" max="9" width="22.109375" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="31" t="s">
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1380,7 +1356,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H3" s="17" t="s">
         <v>20</v>
       </c>
@@ -1391,14 +1367,14 @@
         <v>236</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="32"/>
+      <c r="E4" s="38"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1409,40 +1385,40 @@
         <v>236</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="36"/>
+      <c r="E5" s="40"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="33"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E6" s="32"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="31">
         <v>46091</v>
       </c>
-      <c r="E7" s="33"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E7" s="32"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1456,60 +1432,60 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B26" si="0">B11+1</f>
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1518,7 +1494,7 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1527,7 +1503,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1536,7 +1512,7 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1545,7 +1521,7 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1554,7 +1530,7 @@
       <c r="D18" s="1"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1563,7 +1539,7 @@
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1572,7 +1548,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1581,7 +1557,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1590,7 +1566,7 @@
       <c r="D22" s="1"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1599,7 +1575,7 @@
       <c r="D23" s="1"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1608,7 +1584,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1617,7 +1593,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1626,7 +1602,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C28" s="11" t="s">
         <v>8</v>
       </c>
@@ -1655,37 +1631,37 @@
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J33"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="6"/>
-    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="51.7109375" style="6" customWidth="1"/>
-    <col min="6" max="7" width="8.85546875" style="6"/>
-    <col min="8" max="8" width="11.140625" style="6" customWidth="1"/>
-    <col min="9" max="9" width="26.7109375" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="6"/>
+    <col min="1" max="1" width="8.88671875" style="6"/>
+    <col min="2" max="2" width="12.33203125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="22.5546875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="51.6640625" style="6" customWidth="1"/>
+    <col min="6" max="7" width="8.88671875" style="6"/>
+    <col min="8" max="8" width="11.109375" style="6" customWidth="1"/>
+    <col min="9" max="9" width="26.6640625" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="31" t="s">
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1694,7 +1670,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H3" s="17" t="s">
         <v>20</v>
       </c>
@@ -1705,14 +1681,14 @@
         <v>236</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="40"/>
+      <c r="E4" s="41"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1723,40 +1699,40 @@
         <v>236</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="41" t="s">
+      <c r="D5" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="42"/>
+      <c r="E5" s="43"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="33"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E6" s="32"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="31">
         <v>46091</v>
       </c>
-      <c r="E7" s="33"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E7" s="32"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1770,7 +1746,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="28">
         <v>1</v>
       </c>
@@ -1778,271 +1754,244 @@
         <v>35</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B11" s="28">
-        <f t="shared" ref="B11:B24" si="0">B10+1</f>
+        <f>B10+1</f>
         <v>2</v>
       </c>
       <c r="C11" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="D11" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B12" s="28">
-        <f t="shared" si="0"/>
+        <f>B11+1</f>
         <v>3</v>
       </c>
       <c r="C12" s="24" t="s">
         <v>35</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B13" s="28">
-        <f t="shared" si="0"/>
+        <f>B12+1</f>
         <v>4</v>
       </c>
       <c r="C13" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="24" t="s">
-        <v>54</v>
+      <c r="D13" s="25" t="s">
+        <v>114</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B14" s="28">
-        <f t="shared" si="0"/>
+        <f>B13+1</f>
         <v>5</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="28">
-        <f t="shared" si="0"/>
+        <f>B14+1</f>
         <v>6</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B16" s="28">
-        <f t="shared" si="0"/>
+        <f>B15+1</f>
         <v>7</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>60</v>
+        <v>37</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>42</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B17" s="28">
-        <f t="shared" si="0"/>
+        <f>B16+1</f>
         <v>8</v>
       </c>
       <c r="C17" s="24" t="s">
         <v>37</v>
       </c>
       <c r="D17" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B18" s="28">
+        <f>B17+1</f>
+        <v>9</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B19" s="28">
+        <f>B18+1</f>
+        <v>10</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B20" s="28">
+        <f>B19+1</f>
+        <v>11</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E20" s="27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B21" s="28">
+        <f>B20+1</f>
+        <v>12</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="25" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B18" s="28">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B19" s="28">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="E19" s="27" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="B20" s="28">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" s="27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="28">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>43</v>
-      </c>
       <c r="E21" s="27" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B22" s="28">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="27" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="28">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="E23" s="27" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="B24" s="28">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="E24" s="27" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="28"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="27"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B23" s="28"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="27"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B24" s="28"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="27"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="3"/>
       <c r="C25" s="24"/>
       <c r="D25" s="25"/>
       <c r="E25" s="27"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="3"/>
       <c r="C26" s="24"/>
       <c r="D26" s="25"/>
       <c r="E26" s="27"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="3"/>
       <c r="C27" s="24"/>
       <c r="D27" s="25"/>
       <c r="E27" s="27"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="3"/>
       <c r="C28" s="24"/>
       <c r="D28" s="25"/>
       <c r="E28" s="27"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="3"/>
       <c r="C29" s="24"/>
       <c r="D29" s="25"/>
       <c r="E29" s="27"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="3"/>
       <c r="C30" s="24"/>
       <c r="D30" s="25"/>
       <c r="E30" s="27"/>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="3"/>
       <c r="C31" s="24"/>
       <c r="D31" s="25"/>
       <c r="E31" s="27"/>
     </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C33" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="12"/>
       <c r="E33" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2065,37 +2014,37 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="6"/>
-    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" style="6" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="6"/>
+    <col min="2" max="2" width="12.33203125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="23.5546875" style="6" customWidth="1"/>
     <col min="4" max="4" width="49" style="6" customWidth="1"/>
-    <col min="5" max="5" width="48.85546875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="52.140625" style="6" customWidth="1"/>
-    <col min="7" max="8" width="8.85546875" style="6"/>
-    <col min="9" max="9" width="26.7109375" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="6"/>
+    <col min="5" max="5" width="48.88671875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="52.109375" style="6" customWidth="1"/>
+    <col min="7" max="8" width="8.88671875" style="6"/>
+    <col min="9" max="9" width="26.6640625" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="31" t="s">
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -2104,7 +2053,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H3" s="17" t="s">
         <v>20</v>
       </c>
@@ -2115,14 +2064,14 @@
         <v>236</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C4" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="40" t="s">
-        <v>92</v>
-      </c>
-      <c r="E4" s="40"/>
+      <c r="D4" s="41" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="41"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -2133,32 +2082,32 @@
         <v>236</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="33"/>
+      <c r="E5" s="32"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="31">
         <v>46092</v>
       </c>
-      <c r="E6" s="33"/>
+      <c r="E6" s="32"/>
       <c r="F6" s="20"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -2175,194 +2124,194 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>1</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" s="45" t="s">
-        <v>96</v>
-      </c>
-      <c r="F10" s="45" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="E11" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="F11" s="45" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="36" x14ac:dyDescent="0.25">
+      <c r="E11" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="36" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
       <c r="C12" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="D12" s="24" t="s">
+      <c r="E12" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="30" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B13" s="3">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B14" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14" s="30"/>
+    </row>
+    <row r="15" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B15" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="60" x14ac:dyDescent="0.3">
+      <c r="B16" s="3">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="24" x14ac:dyDescent="0.3">
+      <c r="B17" s="3">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C17" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="E12" s="45" t="s">
-        <v>101</v>
-      </c>
-      <c r="F12" s="45" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B13" s="3">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="D13" s="25" t="s">
+      <c r="D17" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="E17" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="E13" s="45" t="s">
-        <v>104</v>
-      </c>
-      <c r="F13" s="45" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" s="45" t="s">
-        <v>106</v>
-      </c>
-      <c r="F14" s="45"/>
-    </row>
-    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B15" s="3">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="D15" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="B16" s="3">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" s="45" t="s">
-        <v>117</v>
-      </c>
-      <c r="F16" s="45" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="B17" s="3">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="E17" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="F17" s="45"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F17" s="30"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C18" s="24"/>
       <c r="D18" s="25"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C19" s="24"/>
       <c r="D19" s="24"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C20" s="24"/>
       <c r="D20" s="25"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C21" s="24"/>
       <c r="D21" s="24"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C22" s="24"/>
       <c r="D22" s="25"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2372,7 +2321,7 @@
       <c r="E23" s="25"/>
       <c r="F23" s="25"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2382,7 +2331,7 @@
       <c r="E24" s="25"/>
       <c r="F24" s="25"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2392,7 +2341,7 @@
       <c r="E25" s="25"/>
       <c r="F25" s="25"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2402,7 +2351,7 @@
       <c r="E26" s="25"/>
       <c r="F26" s="25"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2412,7 +2361,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2422,7 +2371,7 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2432,7 +2381,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2442,15 +2391,17 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C32" s="43" t="s">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C32" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="44"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="18"/>
-    </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="D32" s="45"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="18" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F35" s="21"/>
     </row>
   </sheetData>

--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -1,21 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TudorStanca\informatica\ubb-anul-3\vvss\lab1\MyDrinkShop\docs\Lab01\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6121A6D6-DF38-44F6-99B9-C88CCC192102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Export Summary" sheetId="1" r:id="rId5"/>
-    <sheet name="Requirements Phase Defects" sheetId="2" r:id="rId6"/>
-    <sheet name="Architect. Design Phase Defects" sheetId="3" r:id="rId7"/>
-    <sheet name="Coding Phase Defects" sheetId="4" r:id="rId8"/>
-    <sheet name="Tool-basedCodeAnalysis" sheetId="5" r:id="rId9"/>
+    <sheet name="Export Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Requirements Phase Defects" sheetId="2" r:id="rId2"/>
+    <sheet name="Architect. Design Phase Defects" sheetId="3" r:id="rId3"/>
+    <sheet name="Coding Phase Defects" sheetId="4" r:id="rId4"/>
+    <sheet name="Tool-basedCodeAnalysis" sheetId="5" r:id="rId5"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -37,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="130">
   <si>
     <t>This document was exported from Numbers. Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -445,11 +470,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
-  </numFmts>
-  <fonts count="12">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -466,54 +488,44 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <u val="single"/>
+      <u/>
       <sz val="12"/>
       <color indexed="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="15"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b val="1"/>
+      <b/>
       <sz val="12"/>
       <color indexed="12"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <i val="1"/>
+      <i/>
       <sz val="9"/>
       <color indexed="15"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="1"/>
+      <b/>
+      <i/>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <i val="1"/>
+      <i/>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <i val="1"/>
+      <i/>
       <sz val="9"/>
       <color indexed="8"/>
       <name val="Consolas"/>
@@ -734,232 +746,176 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+  <cellXfs count="76">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="6" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="6" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="6" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="7" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="7" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="7" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -969,32 +925,85 @@
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ff5e88b1"/>
-      <rgbColor rgb="ffeef3f4"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ff000080"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffaaaaaa"/>
-      <rgbColor rgb="ffc00000"/>
-      <rgbColor rgb="ffe5dfec"/>
-      <rgbColor rgb="fffde9d9"/>
-      <rgbColor rgb="ffd2dae4"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FF5E88B1"/>
+      <rgbColor rgb="FFEEF3F4"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFAAAAAA"/>
+      <rgbColor rgb="FFC00000"/>
+      <rgbColor rgb="FFE5DFEC"/>
+      <rgbColor rgb="FFFDE9D9"/>
+      <rgbColor rgb="FFD2DAE4"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
     <a:clrScheme name="Office Theme 2007 - 2010">
       <a:dk1>
@@ -1120,7 +1129,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
+            <a:outerShdw blurRad="38100" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1129,7 +1138,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
+            <a:outerShdw blurRad="38100" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1138,7 +1147,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+            <a:outerShdw blurRad="38100" dist="20000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -1212,7 +1221,7 @@
           <a:round/>
         </a:ln>
         <a:effectLst>
-          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
+          <a:outerShdw blurRad="38100" dist="23000" dir="5400000" rotWithShape="0">
             <a:srgbClr val="000000">
               <a:alpha val="35000"/>
             </a:srgbClr>
@@ -1220,7 +1229,7 @@
         </a:effectLst>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1238,7 +1247,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1267,7 +1276,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1292,7 +1301,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1317,7 +1326,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1342,7 +1351,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1367,7 +1376,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1392,7 +1401,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1417,7 +1426,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1442,7 +1451,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1467,7 +1476,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1480,9 +1489,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -1497,7 +1512,7 @@
           <a:round/>
         </a:ln>
         <a:effectLst>
-          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+          <a:outerShdw blurRad="38100" dist="20000" dir="5400000" rotWithShape="0">
             <a:srgbClr val="000000">
               <a:alpha val="38000"/>
             </a:srgbClr>
@@ -1505,7 +1520,7 @@
         </a:effectLst>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1523,7 +1538,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1548,7 +1563,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1573,7 +1588,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1598,7 +1613,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1623,7 +1638,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1648,7 +1663,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1673,7 +1688,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1698,7 +1713,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1723,7 +1738,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1748,7 +1763,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1761,9 +1776,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -1777,7 +1798,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1795,7 +1816,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1824,7 +1845,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1849,7 +1870,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1874,7 +1895,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1899,7 +1920,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1924,7 +1945,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1949,7 +1970,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1974,7 +1995,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1999,7 +2020,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2024,7 +2045,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2037,103 +2058,111 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B3:D16"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="4" width="30.5547" customWidth="1"/>
+    <col min="2" max="4" width="30.53515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="0.05" customHeight="1">
-      <c r="B3" t="s" s="1">
+    <row r="3" spans="2:4" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="C3"/>
-      <c r="D3"/>
-    </row>
-    <row r="7">
-      <c r="B7" t="s" s="2">
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+    </row>
+    <row r="7" spans="2:4" ht="18.45" x14ac:dyDescent="0.5">
+      <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C7" t="s" s="2">
+      <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D7" t="s" s="2">
+      <c r="D7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="s" s="3">
+    <row r="9" spans="2:4" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="4"/>
-      <c r="C10" t="s" s="4">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="2:4" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D10" t="s" s="5">
+      <c r="D10" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" t="s" s="3">
+    <row r="11" spans="2:4" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="B11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="4"/>
-      <c r="C12" t="s" s="4">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="2:4" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D12" t="s" s="5">
+      <c r="D12" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" t="s" s="3">
+    <row r="13" spans="2:4" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="B13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="4"/>
-      <c r="C14" t="s" s="4">
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="2:4" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D14" t="s" s="5">
+      <c r="D14" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" t="s" s="3">
+    <row r="15" spans="2:4" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="B15" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="4"/>
-      <c r="C16" t="s" s="4">
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="2:4" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D16" t="s" s="5">
+      <c r="D16" s="4" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2142,496 +2171,498 @@
     <mergeCell ref="B3:D3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D10" location="'Requirements Phase Defects'!R1C1" tooltip="" display="Requirements Phase Defects"/>
-    <hyperlink ref="D12" location="'Architect. Design Phase Defects'!R1C1" tooltip="" display="Architect. Design Phase Defects"/>
-    <hyperlink ref="D14" location="'Coding Phase Defects'!R1C1" tooltip="" display="Coding Phase Defects"/>
-    <hyperlink ref="D16" location="'Tool-basedCodeAnalysis'!R1C1" tooltip="" display="Tool-basedCodeAnalysis"/>
+    <hyperlink ref="D10" location="'Requirements Phase Defects'!R1C1" display="Requirements Phase Defects" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D12" location="'Architect. Design Phase Defects'!R1C1" display="Architect. Design Phase Defects" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D14" location="'Coding Phase Defects'!R1C1" display="Coding Phase Defects" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D16" location="'Tool-basedCodeAnalysis'!R1C1" display="Tool-basedCodeAnalysis" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
   </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="14.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.85156" style="6" customWidth="1"/>
-    <col min="2" max="2" width="12.3516" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.3516" style="6" customWidth="1"/>
-    <col min="4" max="4" width="18.3516" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.5" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.85156" style="6" customWidth="1"/>
-    <col min="9" max="9" width="21" style="6" customWidth="1"/>
-    <col min="10" max="10" width="14.5" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="8.85156" style="6" customWidth="1"/>
+    <col min="1" max="1" width="8.84375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.3828125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.3828125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="18.3828125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="41.4609375" style="5" customWidth="1"/>
+    <col min="6" max="8" width="8.84375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="21" style="5" customWidth="1"/>
+    <col min="10" max="10" width="14.4609375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="8.84375" style="5" customWidth="1"/>
+    <col min="12" max="16384" width="8.84375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" customHeight="1">
-      <c r="A1" s="7"/>
-      <c r="B1" t="s" s="8">
+    <row r="1" spans="1:10" ht="15.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="6"/>
+      <c r="B1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="10"/>
-      <c r="H1" t="s" s="11">
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-    </row>
-    <row r="2" ht="13.55" customHeight="1">
-      <c r="A2" s="9"/>
-      <c r="B2" t="s" s="13">
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+    </row>
+    <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="8"/>
+      <c r="B2" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="15"/>
-      <c r="I2" t="s" s="16">
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s" s="16">
+      <c r="J2" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="13.55" customHeight="1">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="10"/>
-      <c r="H3" t="s" s="16">
+    <row r="3" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="I3" t="s" s="18">
+      <c r="I3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="14">
         <v>236</v>
       </c>
     </row>
-    <row r="4" ht="13.55" customHeight="1">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10"/>
-      <c r="C4" t="s" s="20">
+    <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="8"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s" s="21">
+      <c r="D4" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="22"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="10"/>
-      <c r="H4" t="s" s="16">
+      <c r="E4" s="62"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="I4" t="s" s="24">
+      <c r="I4" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="19">
+      <c r="J4" s="14">
         <v>236</v>
       </c>
     </row>
-    <row r="5" ht="13.55" customHeight="1">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10"/>
-      <c r="C5" t="s" s="20">
+    <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D5" t="s" s="25">
+      <c r="D5" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="26"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="10"/>
-      <c r="H5" t="s" s="16">
+      <c r="E5" s="65"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="I5" t="s" s="24">
+      <c r="I5" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="27">
+      <c r="J5" s="18">
         <v>236</v>
       </c>
     </row>
-    <row r="6" ht="13.55" customHeight="1">
-      <c r="A6" s="9"/>
-      <c r="B6" s="28"/>
-      <c r="C6" t="s" s="29">
+    <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="8"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D6" t="s" s="24">
+      <c r="D6" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-    </row>
-    <row r="7" ht="13.55" customHeight="1">
-      <c r="A7" s="9"/>
-      <c r="B7" s="10"/>
-      <c r="C7" t="s" s="29">
+      <c r="E6" s="56"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+    </row>
+    <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="8"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="55">
         <v>46091</v>
       </c>
-      <c r="E7" s="30"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-    </row>
-    <row r="8" ht="13.55" customHeight="1">
-      <c r="A8" s="9"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-    </row>
-    <row r="9" ht="13.55" customHeight="1">
-      <c r="A9" s="10"/>
-      <c r="B9" t="s" s="34">
+      <c r="E7" s="56"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="8"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="9"/>
+      <c r="B9" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C9" t="s" s="34">
+      <c r="C9" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="D9" t="s" s="34">
+      <c r="D9" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="E9" t="s" s="35">
+      <c r="E9" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="23"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-    </row>
-    <row r="10" ht="43.2" customHeight="1">
-      <c r="A10" s="10"/>
-      <c r="B10" s="36">
+      <c r="F9" s="16"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="9"/>
+      <c r="B10" s="25">
         <v>1</v>
       </c>
-      <c r="C10" t="s" s="37">
+      <c r="C10" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="D10" t="s" s="37">
+      <c r="D10" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E10" t="s" s="38">
+      <c r="E10" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="23"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-    </row>
-    <row r="11" ht="28.8" customHeight="1">
-      <c r="A11" s="10"/>
-      <c r="B11" s="36" cm="1">
+      <c r="F10" s="16"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="1:10" ht="28.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="9"/>
+      <c r="B11" s="25" cm="1">
         <f t="array" ref="B11">B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" t="s" s="37">
+      <c r="C11" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="39"/>
-      <c r="E11" t="s" s="38">
+      <c r="D11" s="28"/>
+      <c r="E11" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="23"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-    </row>
-    <row r="12" ht="43.2" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="36" cm="1">
+      <c r="F11" s="16"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="9"/>
+      <c r="B12" s="25" cm="1">
         <f t="array" ref="B12">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" t="s" s="37">
+      <c r="C12" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="39"/>
-      <c r="E12" t="s" s="38">
+      <c r="D12" s="28"/>
+      <c r="E12" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="23"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-    </row>
-    <row r="13" ht="57.6" customHeight="1">
-      <c r="A13" s="10"/>
-      <c r="B13" s="36" cm="1">
+      <c r="F12" s="16"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" ht="57.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="9"/>
+      <c r="B13" s="25" cm="1">
         <f t="array" ref="B13">B12+1</f>
         <v>4</v>
       </c>
-      <c r="C13" t="s" s="37">
+      <c r="C13" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="39"/>
-      <c r="E13" t="s" s="38">
+      <c r="D13" s="28"/>
+      <c r="E13" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="23"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-    </row>
-    <row r="14" ht="43.2" customHeight="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="36" cm="1">
+      <c r="F13" s="16"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+    </row>
+    <row r="14" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="9"/>
+      <c r="B14" s="25" cm="1">
         <f t="array" ref="B14">B13+1</f>
         <v>5</v>
       </c>
-      <c r="C14" t="s" s="37">
+      <c r="C14" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="39"/>
-      <c r="E14" t="s" s="38">
+      <c r="D14" s="28"/>
+      <c r="E14" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="23"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-    </row>
-    <row r="15" ht="13.55" customHeight="1">
-      <c r="A15" s="10"/>
-      <c r="B15" s="36" cm="1">
+      <c r="F14" s="16"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="9"/>
+      <c r="B15" s="25" cm="1">
         <f t="array" ref="B15">B14+1</f>
         <v>6</v>
       </c>
-      <c r="C15" t="s" s="37">
+      <c r="C15" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="39"/>
-      <c r="E15" t="s" s="38">
+      <c r="D15" s="28"/>
+      <c r="E15" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="F15" t="s" s="40">
+      <c r="F15" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-    </row>
-    <row r="16" ht="13.55" customHeight="1">
-      <c r="A16" s="10"/>
-      <c r="B16" s="36" cm="1">
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+    </row>
+    <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="9"/>
+      <c r="B16" s="25" cm="1">
         <f t="array" ref="B16">B15+1</f>
         <v>7</v>
       </c>
-      <c r="C16" t="s" s="37">
+      <c r="C16" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="39"/>
-      <c r="E16" t="s" s="38">
+      <c r="D16" s="28"/>
+      <c r="E16" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="23"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-    </row>
-    <row r="17" ht="26.55" customHeight="1">
-      <c r="A17" s="10"/>
-      <c r="B17" s="36" cm="1">
+      <c r="F16" s="16"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="1:10" ht="26.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="9"/>
+      <c r="B17" s="25" cm="1">
         <f t="array" ref="B17">B16+1</f>
         <v>8</v>
       </c>
-      <c r="C17" t="s" s="37">
+      <c r="C17" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="39"/>
-      <c r="E17" t="s" s="38">
+      <c r="D17" s="28"/>
+      <c r="E17" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="23"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-    </row>
-    <row r="18" ht="13.55" customHeight="1">
-      <c r="A18" s="10"/>
-      <c r="B18" s="36" cm="1">
+      <c r="F17" s="16"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+    </row>
+    <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="9"/>
+      <c r="B18" s="25" cm="1">
         <f t="array" ref="B18">B17+1</f>
         <v>9</v>
       </c>
-      <c r="C18" t="s" s="16">
+      <c r="C18" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="15"/>
-      <c r="E18" t="s" s="41">
+      <c r="D18" s="10"/>
+      <c r="E18" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="23"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-    </row>
-    <row r="19" ht="13.55" customHeight="1">
-      <c r="A19" s="10"/>
-      <c r="B19" s="36" cm="1">
+      <c r="F18" s="16"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+    </row>
+    <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="9"/>
+      <c r="B19" s="25" cm="1">
         <f t="array" ref="B19">B18+1</f>
         <v>10</v>
       </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-    </row>
-    <row r="20" ht="13.55" customHeight="1">
-      <c r="A20" s="10"/>
-      <c r="B20" s="36" cm="1">
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+    </row>
+    <row r="20" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="9"/>
+      <c r="B20" s="25" cm="1">
         <f t="array" ref="B20">B19+1</f>
         <v>11</v>
       </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-    </row>
-    <row r="21" ht="13.55" customHeight="1">
-      <c r="A21" s="10"/>
-      <c r="B21" s="36" cm="1">
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+    </row>
+    <row r="21" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="9"/>
+      <c r="B21" s="25" cm="1">
         <f t="array" ref="B21">B20+1</f>
         <v>12</v>
       </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-    </row>
-    <row r="22" ht="13.55" customHeight="1">
-      <c r="A22" s="10"/>
-      <c r="B22" s="36" cm="1">
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+    </row>
+    <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="9"/>
+      <c r="B22" s="25" cm="1">
         <f t="array" ref="B22">B21+1</f>
         <v>13</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-    </row>
-    <row r="23" ht="13.55" customHeight="1">
-      <c r="A23" s="10"/>
-      <c r="B23" s="36" cm="1">
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+    </row>
+    <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="9"/>
+      <c r="B23" s="25" cm="1">
         <f t="array" ref="B23">B22+1</f>
         <v>14</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-    </row>
-    <row r="24" ht="13.55" customHeight="1">
-      <c r="A24" s="10"/>
-      <c r="B24" s="36" cm="1">
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+    </row>
+    <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="9"/>
+      <c r="B24" s="25" cm="1">
         <f t="array" ref="B24">B23+1</f>
         <v>15</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-    </row>
-    <row r="25" ht="13.55" customHeight="1">
-      <c r="A25" s="10"/>
-      <c r="B25" s="36" cm="1">
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+    </row>
+    <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="9"/>
+      <c r="B25" s="25" cm="1">
         <f t="array" ref="B25">B24+1</f>
         <v>16</v>
       </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-    </row>
-    <row r="26" ht="13.55" customHeight="1">
-      <c r="A26" s="9"/>
-      <c r="B26" s="31"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-    </row>
-    <row r="27" ht="13.55" customHeight="1">
-      <c r="A27" s="9"/>
-      <c r="B27" s="10"/>
-      <c r="C27" t="s" s="43">
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+    </row>
+    <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="8"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+    </row>
+    <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="8"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="44"/>
-      <c r="E27" t="s" s="37">
+      <c r="D27" s="33"/>
+      <c r="E27" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="F27" s="23"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2643,7 +2674,7 @@
     <mergeCell ref="D5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
@@ -2651,480 +2682,480 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="14.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.85156" style="45" customWidth="1"/>
-    <col min="2" max="2" width="12.3516" style="45" customWidth="1"/>
-    <col min="3" max="3" width="16.3516" style="45" customWidth="1"/>
-    <col min="4" max="4" width="16.5" style="45" customWidth="1"/>
-    <col min="5" max="5" width="41.5" style="45" customWidth="1"/>
-    <col min="6" max="8" width="8.85156" style="45" customWidth="1"/>
-    <col min="9" max="9" width="22.1719" style="45" customWidth="1"/>
-    <col min="10" max="10" width="8.85156" style="45" customWidth="1"/>
-    <col min="11" max="16384" width="8.85156" style="45" customWidth="1"/>
+    <col min="1" max="1" width="8.84375" style="34" customWidth="1"/>
+    <col min="2" max="2" width="12.3828125" style="34" customWidth="1"/>
+    <col min="3" max="3" width="16.3828125" style="34" customWidth="1"/>
+    <col min="4" max="4" width="16.4609375" style="34" customWidth="1"/>
+    <col min="5" max="5" width="41.4609375" style="34" customWidth="1"/>
+    <col min="6" max="8" width="8.84375" style="34" customWidth="1"/>
+    <col min="9" max="9" width="22.15234375" style="34" customWidth="1"/>
+    <col min="10" max="11" width="8.84375" style="34" customWidth="1"/>
+    <col min="12" max="16384" width="8.84375" style="34"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" customHeight="1">
-      <c r="A1" s="7"/>
-      <c r="B1" t="s" s="8">
+    <row r="1" spans="1:10" ht="15.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="6"/>
+      <c r="B1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="10"/>
-      <c r="H1" t="s" s="11">
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-    </row>
-    <row r="2" ht="13.55" customHeight="1">
-      <c r="A2" s="9"/>
-      <c r="B2" t="s" s="13">
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+    </row>
+    <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="8"/>
+      <c r="B2" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="15"/>
-      <c r="I2" t="s" s="16">
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s" s="16">
+      <c r="J2" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="13.55" customHeight="1">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="10"/>
-      <c r="H3" t="s" s="16">
+    <row r="3" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="I3" t="s" s="18">
+      <c r="I3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="14">
         <v>236</v>
       </c>
     </row>
-    <row r="4" ht="13.55" customHeight="1">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10"/>
-      <c r="C4" t="s" s="46">
+    <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="8"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s" s="47">
+      <c r="D4" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="48"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="10"/>
-      <c r="H4" t="s" s="16">
+      <c r="E4" s="67"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="I4" t="s" s="24">
+      <c r="I4" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="19">
+      <c r="J4" s="14">
         <v>236</v>
       </c>
     </row>
-    <row r="5" ht="13.55" customHeight="1">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10"/>
-      <c r="C5" t="s" s="46">
+    <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="D5" t="s" s="49">
+      <c r="D5" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="50"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="10"/>
-      <c r="H5" t="s" s="16">
+      <c r="E5" s="69"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="I5" t="s" s="24">
+      <c r="I5" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="19">
+      <c r="J5" s="14">
         <v>236</v>
       </c>
     </row>
-    <row r="6" ht="13.55" customHeight="1">
-      <c r="A6" s="9"/>
-      <c r="B6" s="28"/>
-      <c r="C6" t="s" s="29">
+    <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="8"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D6" t="s" s="24">
+      <c r="D6" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-    </row>
-    <row r="7" ht="13.55" customHeight="1">
-      <c r="A7" s="9"/>
-      <c r="B7" s="10"/>
-      <c r="C7" t="s" s="29">
+      <c r="E6" s="56"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+    </row>
+    <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="8"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="55">
         <v>46091</v>
       </c>
-      <c r="E7" s="30"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-    </row>
-    <row r="8" ht="13.55" customHeight="1">
-      <c r="A8" s="9"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-    </row>
-    <row r="9" ht="13.55" customHeight="1">
-      <c r="A9" s="10"/>
-      <c r="B9" t="s" s="34">
+      <c r="E7" s="56"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="8"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="9"/>
+      <c r="B9" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C9" t="s" s="34">
+      <c r="C9" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="D9" t="s" s="34">
+      <c r="D9" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="E9" t="s" s="34">
+      <c r="E9" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="23"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-    </row>
-    <row r="10" ht="57.6" customHeight="1">
-      <c r="A10" s="10"/>
-      <c r="B10" s="36">
+      <c r="F9" s="16"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" ht="57.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="9"/>
+      <c r="B10" s="25">
         <v>1</v>
       </c>
-      <c r="C10" t="s" s="37">
+      <c r="C10" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="D10" t="s" s="38">
+      <c r="D10" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="E10" t="s" s="38">
+      <c r="E10" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="23"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-    </row>
-    <row r="11" ht="43.2" customHeight="1">
-      <c r="A11" s="10"/>
-      <c r="B11" s="36" cm="1">
+      <c r="F10" s="16"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="9"/>
+      <c r="B11" s="25" cm="1">
         <f t="array" ref="B11">B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" t="s" s="37">
+      <c r="C11" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="51"/>
-      <c r="E11" t="s" s="38">
+      <c r="D11" s="36"/>
+      <c r="E11" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="23"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-    </row>
-    <row r="12" ht="28.8" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="36" cm="1">
+      <c r="F11" s="16"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="1:10" ht="28.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="9"/>
+      <c r="B12" s="25" cm="1">
         <f t="array" ref="B12">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" t="s" s="37">
+      <c r="C12" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="39"/>
-      <c r="E12" t="s" s="38">
+      <c r="D12" s="28"/>
+      <c r="E12" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="F12" s="23"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-    </row>
-    <row r="13" ht="43.2" customHeight="1">
-      <c r="A13" s="10"/>
-      <c r="B13" s="36" cm="1">
+      <c r="F12" s="16"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="9"/>
+      <c r="B13" s="25" cm="1">
         <f t="array" ref="B13">B12+1</f>
         <v>4</v>
       </c>
-      <c r="C13" t="s" s="37">
+      <c r="C13" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="39"/>
-      <c r="E13" t="s" s="38">
+      <c r="D13" s="28"/>
+      <c r="E13" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="23"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-    </row>
-    <row r="14" ht="13.55" customHeight="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="36" cm="1">
+      <c r="F13" s="16"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+    </row>
+    <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="9"/>
+      <c r="B14" s="25" cm="1">
         <f t="array" ref="B14">B13+1</f>
         <v>5</v>
       </c>
-      <c r="C14" s="39"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-    </row>
-    <row r="15" ht="13.55" customHeight="1">
-      <c r="A15" s="10"/>
-      <c r="B15" s="36" cm="1">
+      <c r="C14" s="28"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="9"/>
+      <c r="B15" s="25" cm="1">
         <f t="array" ref="B15">B14+1</f>
         <v>6</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-    </row>
-    <row r="16" ht="13.55" customHeight="1">
-      <c r="A16" s="10"/>
-      <c r="B16" s="36" cm="1">
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+    </row>
+    <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="9"/>
+      <c r="B16" s="25" cm="1">
         <f t="array" ref="B16">B15+1</f>
         <v>7</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-    </row>
-    <row r="17" ht="13.55" customHeight="1">
-      <c r="A17" s="10"/>
-      <c r="B17" s="36" cm="1">
+      <c r="C16" s="28"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="9"/>
+      <c r="B17" s="25" cm="1">
         <f t="array" ref="B17">B16+1</f>
         <v>8</v>
       </c>
-      <c r="C17" s="39"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-    </row>
-    <row r="18" ht="13.55" customHeight="1">
-      <c r="A18" s="10"/>
-      <c r="B18" s="36" cm="1">
+      <c r="C17" s="28"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+    </row>
+    <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="9"/>
+      <c r="B18" s="25" cm="1">
         <f t="array" ref="B18">B17+1</f>
         <v>9</v>
       </c>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-    </row>
-    <row r="19" ht="13.55" customHeight="1">
-      <c r="A19" s="10"/>
-      <c r="B19" s="36" cm="1">
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+    </row>
+    <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="9"/>
+      <c r="B19" s="25" cm="1">
         <f t="array" ref="B19">B18+1</f>
         <v>10</v>
       </c>
-      <c r="C19" s="39"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-    </row>
-    <row r="20" ht="13.55" customHeight="1">
-      <c r="A20" s="10"/>
-      <c r="B20" s="36" cm="1">
+      <c r="C19" s="28"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+    </row>
+    <row r="20" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="9"/>
+      <c r="B20" s="25" cm="1">
         <f t="array" ref="B20">B19+1</f>
         <v>11</v>
       </c>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-    </row>
-    <row r="21" ht="13.55" customHeight="1">
-      <c r="A21" s="10"/>
-      <c r="B21" s="36" cm="1">
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+    </row>
+    <row r="21" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="9"/>
+      <c r="B21" s="25" cm="1">
         <f t="array" ref="B21">B20+1</f>
         <v>12</v>
       </c>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-    </row>
-    <row r="22" ht="13.55" customHeight="1">
-      <c r="A22" s="10"/>
-      <c r="B22" s="36" cm="1">
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+    </row>
+    <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="9"/>
+      <c r="B22" s="25" cm="1">
         <f t="array" ref="B22">B21+1</f>
         <v>13</v>
       </c>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-    </row>
-    <row r="23" ht="13.55" customHeight="1">
-      <c r="A23" s="10"/>
-      <c r="B23" s="36" cm="1">
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+    </row>
+    <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="9"/>
+      <c r="B23" s="25" cm="1">
         <f t="array" ref="B23">B22+1</f>
         <v>14</v>
       </c>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-    </row>
-    <row r="24" ht="13.55" customHeight="1">
-      <c r="A24" s="10"/>
-      <c r="B24" s="36" cm="1">
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+    </row>
+    <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="9"/>
+      <c r="B24" s="25" cm="1">
         <f t="array" ref="B24">B23+1</f>
         <v>15</v>
       </c>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-    </row>
-    <row r="25" ht="13.55" customHeight="1">
-      <c r="A25" s="10"/>
-      <c r="B25" s="36" cm="1">
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+    </row>
+    <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="9"/>
+      <c r="B25" s="25" cm="1">
         <f t="array" ref="B25">B24+1</f>
         <v>16</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-    </row>
-    <row r="26" ht="13.55" customHeight="1">
-      <c r="A26" s="10"/>
-      <c r="B26" s="36" cm="1">
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+    </row>
+    <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="9"/>
+      <c r="B26" s="25" cm="1">
         <f t="array" ref="B26">B25+1</f>
         <v>17</v>
       </c>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-    </row>
-    <row r="27" ht="13.55" customHeight="1">
-      <c r="A27" s="9"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-    </row>
-    <row r="28" ht="13.55" customHeight="1">
-      <c r="A28" s="9"/>
-      <c r="B28" s="10"/>
-      <c r="C28" t="s" s="43">
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+    </row>
+    <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="8"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+    </row>
+    <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="8"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D28" s="44"/>
-      <c r="E28" s="52">
+      <c r="D28" s="33"/>
+      <c r="E28" s="37">
         <v>1</v>
       </c>
-      <c r="F28" s="23"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3136,7 +3167,7 @@
     <mergeCell ref="D5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
@@ -3144,580 +3175,580 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J33"/>
-  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="14.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.85156" style="53" customWidth="1"/>
-    <col min="2" max="2" width="12.3516" style="53" customWidth="1"/>
-    <col min="3" max="3" width="16.3516" style="53" customWidth="1"/>
-    <col min="4" max="4" width="22.5" style="53" customWidth="1"/>
-    <col min="5" max="5" width="51.6719" style="53" customWidth="1"/>
-    <col min="6" max="7" width="8.85156" style="53" customWidth="1"/>
-    <col min="8" max="8" width="11.1719" style="53" customWidth="1"/>
-    <col min="9" max="9" width="26.6719" style="53" customWidth="1"/>
-    <col min="10" max="10" width="8.85156" style="53" customWidth="1"/>
-    <col min="11" max="16384" width="8.85156" style="53" customWidth="1"/>
+    <col min="1" max="1" width="8.84375" style="38" customWidth="1"/>
+    <col min="2" max="2" width="12.3828125" style="38" customWidth="1"/>
+    <col min="3" max="3" width="16.3828125" style="38" customWidth="1"/>
+    <col min="4" max="4" width="22.4609375" style="38" customWidth="1"/>
+    <col min="5" max="5" width="51.69140625" style="38" customWidth="1"/>
+    <col min="6" max="7" width="8.84375" style="38" customWidth="1"/>
+    <col min="8" max="8" width="11.15234375" style="38" customWidth="1"/>
+    <col min="9" max="9" width="26.69140625" style="38" customWidth="1"/>
+    <col min="10" max="11" width="8.84375" style="38" customWidth="1"/>
+    <col min="12" max="16384" width="8.84375" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" customHeight="1">
-      <c r="A1" s="7"/>
-      <c r="B1" t="s" s="8">
+    <row r="1" spans="1:10" ht="15.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="6"/>
+      <c r="B1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="10"/>
-      <c r="H1" t="s" s="11">
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-    </row>
-    <row r="2" ht="13.55" customHeight="1">
-      <c r="A2" s="9"/>
-      <c r="B2" t="s" s="13">
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+    </row>
+    <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="8"/>
+      <c r="B2" s="59" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="15"/>
-      <c r="I2" t="s" s="16">
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s" s="16">
+      <c r="J2" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="13.55" customHeight="1">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="10"/>
-      <c r="H3" t="s" s="16">
+    <row r="3" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="I3" t="s" s="18">
+      <c r="I3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="14">
         <v>236</v>
       </c>
     </row>
-    <row r="4" ht="13.55" customHeight="1">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10"/>
-      <c r="C4" t="s" s="54">
+    <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="8"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s" s="55">
+      <c r="D4" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="E4" s="56"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="10"/>
-      <c r="H4" t="s" s="16">
+      <c r="E4" s="71"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="I4" t="s" s="24">
+      <c r="I4" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="19">
+      <c r="J4" s="14">
         <v>236</v>
       </c>
     </row>
-    <row r="5" ht="13.55" customHeight="1">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10"/>
-      <c r="C5" t="s" s="54">
+    <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="D5" t="s" s="57">
+      <c r="D5" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="E5" s="58"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="10"/>
-      <c r="H5" t="s" s="16">
+      <c r="E5" s="73"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="I5" t="s" s="24">
+      <c r="I5" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="19">
+      <c r="J5" s="14">
         <v>236</v>
       </c>
     </row>
-    <row r="6" ht="13.55" customHeight="1">
-      <c r="A6" s="9"/>
-      <c r="B6" s="28"/>
-      <c r="C6" t="s" s="29">
+    <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="8"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D6" t="s" s="24">
+      <c r="D6" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-    </row>
-    <row r="7" ht="13.55" customHeight="1">
-      <c r="A7" s="9"/>
-      <c r="B7" s="10"/>
-      <c r="C7" t="s" s="29">
+      <c r="E6" s="56"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+    </row>
+    <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="8"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="55">
         <v>46091</v>
       </c>
-      <c r="E7" s="30"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-    </row>
-    <row r="8" ht="13.55" customHeight="1">
-      <c r="A8" s="9"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-    </row>
-    <row r="9" ht="13.55" customHeight="1">
-      <c r="A9" s="10"/>
-      <c r="B9" t="s" s="34">
+      <c r="E7" s="56"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="8"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="9"/>
+      <c r="B9" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C9" t="s" s="34">
+      <c r="C9" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="D9" t="s" s="34">
+      <c r="D9" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="E9" t="s" s="34">
+      <c r="E9" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="23"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-    </row>
-    <row r="10" ht="35.25" customHeight="1">
-      <c r="A10" s="10"/>
-      <c r="B10" s="59">
+      <c r="F9" s="16"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="9"/>
+      <c r="B10" s="40">
         <v>1</v>
       </c>
-      <c r="C10" t="s" s="60">
+      <c r="C10" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="D10" t="s" s="61">
+      <c r="D10" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="E10" t="s" s="62">
+      <c r="E10" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="F10" s="23"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-    </row>
-    <row r="11" ht="28.8" customHeight="1">
-      <c r="A11" s="10"/>
-      <c r="B11" s="59" cm="1">
+      <c r="F10" s="16"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="1:10" ht="28.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="9"/>
+      <c r="B11" s="40" cm="1">
         <f t="array" ref="B11">B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" t="s" s="60">
+      <c r="C11" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="D11" t="s" s="60">
+      <c r="D11" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="E11" t="s" s="63">
+      <c r="E11" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="23"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-    </row>
-    <row r="12" ht="28.8" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="59" cm="1">
+      <c r="F11" s="16"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="1:10" ht="28.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="9"/>
+      <c r="B12" s="40" cm="1">
         <f t="array" ref="B12">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" t="s" s="60">
+      <c r="C12" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="D12" t="s" s="61">
+      <c r="D12" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="E12" t="s" s="63">
+      <c r="E12" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="23"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-    </row>
-    <row r="13" ht="28.8" customHeight="1">
-      <c r="A13" s="10"/>
-      <c r="B13" s="59" cm="1">
+      <c r="F12" s="16"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" ht="28.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="9"/>
+      <c r="B13" s="40" cm="1">
         <f t="array" ref="B13">B12+1</f>
         <v>4</v>
       </c>
-      <c r="C13" t="s" s="60">
+      <c r="C13" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="D13" t="s" s="61">
+      <c r="D13" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="E13" t="s" s="63">
+      <c r="E13" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="F13" s="23"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-    </row>
-    <row r="14" ht="28.8" customHeight="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="59" cm="1">
+      <c r="F13" s="16"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+    </row>
+    <row r="14" spans="1:10" ht="28.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="9"/>
+      <c r="B14" s="40" cm="1">
         <f t="array" ref="B14">B13+1</f>
         <v>5</v>
       </c>
-      <c r="C14" t="s" s="60">
+      <c r="C14" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="D14" t="s" s="61">
+      <c r="D14" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="E14" t="s" s="63">
+      <c r="E14" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="F14" s="23"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-    </row>
-    <row r="15" ht="13.55" customHeight="1">
-      <c r="A15" s="10"/>
-      <c r="B15" s="59" cm="1">
+      <c r="F14" s="16"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="9"/>
+      <c r="B15" s="40" cm="1">
         <f t="array" ref="B15">B14+1</f>
         <v>6</v>
       </c>
-      <c r="C15" t="s" s="60">
+      <c r="C15" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="D15" t="s" s="61">
+      <c r="D15" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="E15" t="s" s="63">
+      <c r="E15" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-    </row>
-    <row r="16" ht="28.8" customHeight="1">
-      <c r="A16" s="10"/>
-      <c r="B16" s="59" cm="1">
+      <c r="F15" s="16"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+    </row>
+    <row r="16" spans="1:10" ht="28.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="9"/>
+      <c r="B16" s="40" cm="1">
         <f t="array" ref="B16">B15+1</f>
         <v>7</v>
       </c>
-      <c r="C16" t="s" s="60">
+      <c r="C16" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="D16" t="s" s="60">
+      <c r="D16" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="E16" t="s" s="63">
+      <c r="E16" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="F16" s="23"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-    </row>
-    <row r="17" ht="28.8" customHeight="1">
-      <c r="A17" s="10"/>
-      <c r="B17" s="59" cm="1">
+      <c r="F16" s="16"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="1:10" ht="28.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="9"/>
+      <c r="B17" s="40" cm="1">
         <f t="array" ref="B17">B16+1</f>
         <v>8</v>
       </c>
-      <c r="C17" t="s" s="60">
+      <c r="C17" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="D17" t="s" s="61">
+      <c r="D17" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="E17" t="s" s="63">
+      <c r="E17" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="F17" s="23"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-    </row>
-    <row r="18" ht="43.2" customHeight="1">
-      <c r="A18" s="10"/>
-      <c r="B18" s="59" cm="1">
+      <c r="F17" s="16"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+    </row>
+    <row r="18" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="9"/>
+      <c r="B18" s="40" cm="1">
         <f t="array" ref="B18">B17+1</f>
         <v>9</v>
       </c>
-      <c r="C18" t="s" s="60">
+      <c r="C18" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="D18" t="s" s="61">
+      <c r="D18" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="E18" t="s" s="63">
+      <c r="E18" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="23"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-    </row>
-    <row r="19" ht="13.55" customHeight="1">
-      <c r="A19" s="10"/>
-      <c r="B19" s="59" cm="1">
+      <c r="F18" s="16"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+    </row>
+    <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="9"/>
+      <c r="B19" s="40" cm="1">
         <f t="array" ref="B19">B18+1</f>
         <v>10</v>
       </c>
-      <c r="C19" t="s" s="60">
+      <c r="C19" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="D19" t="s" s="60">
+      <c r="D19" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="E19" t="s" s="63">
+      <c r="E19" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F19" s="23"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-    </row>
-    <row r="20" ht="28.8" customHeight="1">
-      <c r="A20" s="10"/>
-      <c r="B20" s="59" cm="1">
+      <c r="F19" s="16"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+    </row>
+    <row r="20" spans="1:10" ht="28.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="9"/>
+      <c r="B20" s="40" cm="1">
         <f t="array" ref="B20">B19+1</f>
         <v>11</v>
       </c>
-      <c r="C20" t="s" s="60">
+      <c r="C20" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D20" t="s" s="61">
+      <c r="D20" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="E20" t="s" s="63">
+      <c r="E20" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="F20" s="23"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-    </row>
-    <row r="21" ht="13.55" customHeight="1">
-      <c r="A21" s="10"/>
-      <c r="B21" s="59" cm="1">
+      <c r="F20" s="16"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+    </row>
+    <row r="21" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="9"/>
+      <c r="B21" s="40" cm="1">
         <f t="array" ref="B21">B20+1</f>
         <v>12</v>
       </c>
-      <c r="C21" t="s" s="60">
+      <c r="C21" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="D21" t="s" s="61">
+      <c r="D21" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="E21" t="s" s="63">
+      <c r="E21" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="F21" s="23"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-    </row>
-    <row r="22" ht="13.55" customHeight="1">
-      <c r="A22" s="10"/>
-      <c r="B22" s="64"/>
-      <c r="C22" s="65"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-    </row>
-    <row r="23" ht="13.55" customHeight="1">
-      <c r="A23" s="10"/>
-      <c r="B23" s="64"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="66"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-    </row>
-    <row r="24" ht="13.55" customHeight="1">
-      <c r="A24" s="10"/>
-      <c r="B24" s="64"/>
-      <c r="C24" s="65"/>
-      <c r="D24" s="66"/>
-      <c r="E24" s="67"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-    </row>
-    <row r="25" ht="13.55" customHeight="1">
-      <c r="A25" s="10"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="65"/>
-      <c r="D25" s="66"/>
-      <c r="E25" s="67"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-    </row>
-    <row r="26" ht="13.55" customHeight="1">
-      <c r="A26" s="10"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="65"/>
-      <c r="D26" s="66"/>
-      <c r="E26" s="67"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-    </row>
-    <row r="27" ht="13.55" customHeight="1">
-      <c r="A27" s="10"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="65"/>
-      <c r="D27" s="66"/>
-      <c r="E27" s="67"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-    </row>
-    <row r="28" ht="13.55" customHeight="1">
-      <c r="A28" s="10"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="65"/>
-      <c r="D28" s="66"/>
-      <c r="E28" s="67"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-    </row>
-    <row r="29" ht="13.55" customHeight="1">
-      <c r="A29" s="10"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="65"/>
-      <c r="D29" s="66"/>
-      <c r="E29" s="67"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-    </row>
-    <row r="30" ht="13.55" customHeight="1">
-      <c r="A30" s="10"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="65"/>
-      <c r="D30" s="66"/>
-      <c r="E30" s="67"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-    </row>
-    <row r="31" ht="13.55" customHeight="1">
-      <c r="A31" s="10"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="65"/>
-      <c r="D31" s="66"/>
-      <c r="E31" s="67"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-    </row>
-    <row r="32" ht="13.55" customHeight="1">
-      <c r="A32" s="9"/>
-      <c r="B32" s="31"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-    </row>
-    <row r="33" ht="13.55" customHeight="1">
-      <c r="A33" s="9"/>
-      <c r="B33" s="10"/>
-      <c r="C33" t="s" s="43">
+      <c r="F21" s="16"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+    </row>
+    <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="9"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+    </row>
+    <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="9"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+    </row>
+    <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="9"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+    </row>
+    <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="9"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+    </row>
+    <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="9"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+    </row>
+    <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="9"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+    </row>
+    <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="9"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+    </row>
+    <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="9"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="46"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+    </row>
+    <row r="30" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="9"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="46"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+    </row>
+    <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="9"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+    </row>
+    <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="8"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+    </row>
+    <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="8"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D33" s="44"/>
-      <c r="E33" s="52">
+      <c r="D33" s="33"/>
+      <c r="E33" s="37">
         <v>1</v>
       </c>
-      <c r="F33" s="23"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3729,7 +3760,7 @@
     <mergeCell ref="D5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
@@ -3737,615 +3768,615 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="14.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.85156" style="68" customWidth="1"/>
-    <col min="2" max="2" width="12.3516" style="68" customWidth="1"/>
-    <col min="3" max="3" width="23.5" style="68" customWidth="1"/>
-    <col min="4" max="4" width="49" style="68" customWidth="1"/>
-    <col min="5" max="5" width="48.8516" style="68" customWidth="1"/>
-    <col min="6" max="6" width="52.1719" style="68" customWidth="1"/>
-    <col min="7" max="8" width="8.85156" style="68" customWidth="1"/>
-    <col min="9" max="9" width="26.6719" style="68" customWidth="1"/>
-    <col min="10" max="10" width="8.85156" style="68" customWidth="1"/>
-    <col min="11" max="16384" width="8.85156" style="68" customWidth="1"/>
+    <col min="1" max="1" width="8.84375" style="49" customWidth="1"/>
+    <col min="2" max="2" width="12.3828125" style="49" customWidth="1"/>
+    <col min="3" max="3" width="23.4609375" style="49" customWidth="1"/>
+    <col min="4" max="4" width="49" style="49" customWidth="1"/>
+    <col min="5" max="5" width="48.84375" style="49" customWidth="1"/>
+    <col min="6" max="6" width="52.15234375" style="49" customWidth="1"/>
+    <col min="7" max="8" width="8.84375" style="49" customWidth="1"/>
+    <col min="9" max="9" width="26.69140625" style="49" customWidth="1"/>
+    <col min="10" max="11" width="8.84375" style="49" customWidth="1"/>
+    <col min="12" max="16384" width="8.84375" style="49"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" customHeight="1">
-      <c r="A1" s="7"/>
-      <c r="B1" t="s" s="8">
+    <row r="1" spans="1:10" ht="15.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="6"/>
+      <c r="B1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="10"/>
-      <c r="H1" t="s" s="11">
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-    </row>
-    <row r="2" ht="13.55" customHeight="1">
-      <c r="A2" s="9"/>
-      <c r="B2" t="s" s="13">
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+    </row>
+    <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="8"/>
+      <c r="B2" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="15"/>
-      <c r="I2" t="s" s="16">
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s" s="16">
+      <c r="J2" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="13.55" customHeight="1">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="10"/>
-      <c r="H3" t="s" s="16">
+    <row r="3" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="I3" t="s" s="18">
+      <c r="I3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="14">
         <v>236</v>
       </c>
     </row>
-    <row r="4" ht="13.55" customHeight="1">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10"/>
-      <c r="C4" t="s" s="54">
+    <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="8"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="D4" t="s" s="55">
+      <c r="D4" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="56"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="10"/>
-      <c r="H4" t="s" s="16">
+      <c r="E4" s="71"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="I4" t="s" s="24">
+      <c r="I4" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="19">
+      <c r="J4" s="14">
         <v>236</v>
       </c>
     </row>
-    <row r="5" ht="13.55" customHeight="1">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10"/>
-      <c r="C5" t="s" s="29">
+    <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D5" t="s" s="24">
+      <c r="D5" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="30"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="10"/>
-      <c r="H5" t="s" s="16">
+      <c r="E5" s="56"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="I5" t="s" s="24">
+      <c r="I5" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="19">
+      <c r="J5" s="14">
         <v>236</v>
       </c>
     </row>
-    <row r="6" ht="13.55" customHeight="1">
-      <c r="A6" s="9"/>
-      <c r="B6" s="28"/>
-      <c r="C6" t="s" s="29">
+    <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="8"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="32">
+      <c r="D6" s="55">
         <v>46092</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-    </row>
-    <row r="7" ht="13.55" customHeight="1">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-    </row>
-    <row r="8" ht="13.55" customHeight="1">
-      <c r="A8" s="9"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-    </row>
-    <row r="9" ht="13.55" customHeight="1">
-      <c r="A9" s="10"/>
-      <c r="B9" t="s" s="34">
+      <c r="E6" s="56"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+    </row>
+    <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="8"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="9"/>
+      <c r="B9" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C9" t="s" s="34">
+      <c r="C9" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="D9" t="s" s="34">
+      <c r="D9" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="E9" t="s" s="34">
+      <c r="E9" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="F9" t="s" s="34">
+      <c r="F9" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="G9" s="23"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-    </row>
-    <row r="10" ht="75" customHeight="1">
-      <c r="A10" s="10"/>
-      <c r="B10" s="36">
+      <c r="G9" s="16"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="9"/>
+      <c r="B10" s="25">
         <v>1</v>
       </c>
-      <c r="C10" t="s" s="60">
+      <c r="C10" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="D10" t="s" s="61">
+      <c r="D10" s="42" t="s">
         <v>101</v>
       </c>
-      <c r="E10" t="s" s="69">
+      <c r="E10" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="F10" t="s" s="69">
+      <c r="F10" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="G10" s="23"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="10"/>
-      <c r="B11" s="36" cm="1">
+      <c r="G10" s="16"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="9"/>
+      <c r="B11" s="25" cm="1">
         <f t="array" ref="B11">B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" t="s" s="60">
+      <c r="C11" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="D11" t="s" s="60">
+      <c r="D11" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="E11" t="s" s="69">
+      <c r="E11" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="F11" t="s" s="69">
+      <c r="F11" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="G11" s="23"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="36" cm="1">
+      <c r="G11" s="16"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="9"/>
+      <c r="B12" s="25" cm="1">
         <f t="array" ref="B12">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" t="s" s="60">
+      <c r="C12" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="D12" t="s" s="60">
+      <c r="D12" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="E12" t="s" s="69">
+      <c r="E12" s="50" t="s">
         <v>110</v>
       </c>
-      <c r="F12" t="s" s="69">
+      <c r="F12" s="50" t="s">
         <v>111</v>
       </c>
-      <c r="G12" s="23"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-    </row>
-    <row r="13" ht="28.8" customHeight="1">
-      <c r="A13" s="10"/>
-      <c r="B13" s="36" cm="1">
+      <c r="G12" s="16"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" ht="28.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="9"/>
+      <c r="B13" s="25" cm="1">
         <f t="array" ref="B13">B12+1</f>
         <v>4</v>
       </c>
-      <c r="C13" t="s" s="60">
+      <c r="C13" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="D13" t="s" s="61">
+      <c r="D13" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="E13" t="s" s="69">
+      <c r="E13" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="F13" t="s" s="69">
+      <c r="F13" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="G13" s="23"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-    </row>
-    <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="36" cm="1">
+      <c r="G13" s="16"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+    </row>
+    <row r="14" spans="1:10" ht="14.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="9"/>
+      <c r="B14" s="25" cm="1">
         <f t="array" ref="B14">B13+1</f>
         <v>5</v>
       </c>
-      <c r="C14" t="s" s="60">
+      <c r="C14" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="D14" t="s" s="61">
+      <c r="D14" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="E14" t="s" s="69">
+      <c r="E14" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="F14" s="70"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-    </row>
-    <row r="15" ht="28.8" customHeight="1">
-      <c r="A15" s="10"/>
-      <c r="B15" s="36" cm="1">
+      <c r="F14" s="51"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:10" ht="28.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="9"/>
+      <c r="B15" s="25" cm="1">
         <f t="array" ref="B15">B14+1</f>
         <v>6</v>
       </c>
-      <c r="C15" t="s" s="60">
+      <c r="C15" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="D15" t="s" s="61">
+      <c r="D15" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="E15" s="70"/>
-      <c r="F15" t="s" s="69">
+      <c r="E15" s="51"/>
+      <c r="F15" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="G15" s="23"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-    </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="10"/>
-      <c r="B16" s="36" cm="1">
+      <c r="G15" s="16"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+    </row>
+    <row r="16" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="9"/>
+      <c r="B16" s="25" cm="1">
         <f t="array" ref="B16">B15+1</f>
         <v>7</v>
       </c>
-      <c r="C16" t="s" s="60">
+      <c r="C16" s="41" t="s">
         <v>122</v>
       </c>
-      <c r="D16" t="s" s="61">
+      <c r="D16" s="42" t="s">
         <v>123</v>
       </c>
-      <c r="E16" t="s" s="69">
+      <c r="E16" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="F16" t="s" s="69">
+      <c r="F16" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="G16" s="23"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="10"/>
-      <c r="B17" s="36" cm="1">
+      <c r="G16" s="16"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="9"/>
+      <c r="B17" s="25" cm="1">
         <f t="array" ref="B17">B16+1</f>
         <v>8</v>
       </c>
-      <c r="C17" t="s" s="60">
+      <c r="C17" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="D17" t="s" s="61">
+      <c r="D17" s="42" t="s">
         <v>127</v>
       </c>
-      <c r="E17" t="s" s="69">
+      <c r="E17" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="F17" s="70"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-    </row>
-    <row r="18" ht="14" customHeight="1">
-      <c r="A18" s="10"/>
-      <c r="B18" s="36" cm="1">
+      <c r="F17" s="51"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+    </row>
+    <row r="18" spans="1:10" ht="14.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="9"/>
+      <c r="B18" s="25" cm="1">
         <f t="array" ref="B18">B17+1</f>
         <v>9</v>
       </c>
-      <c r="C18" s="65"/>
-      <c r="D18" s="66"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="70"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-    </row>
-    <row r="19" ht="14" customHeight="1">
-      <c r="A19" s="10"/>
-      <c r="B19" s="36" cm="1">
+      <c r="C18" s="46"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+    </row>
+    <row r="19" spans="1:10" ht="14.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="9"/>
+      <c r="B19" s="25" cm="1">
         <f t="array" ref="B19">B18+1</f>
         <v>10</v>
       </c>
-      <c r="C19" s="65"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="70"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-    </row>
-    <row r="20" ht="14" customHeight="1">
-      <c r="A20" s="10"/>
-      <c r="B20" s="36" cm="1">
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+    </row>
+    <row r="20" spans="1:10" ht="14.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="9"/>
+      <c r="B20" s="25" cm="1">
         <f t="array" ref="B20">B19+1</f>
         <v>11</v>
       </c>
-      <c r="C20" s="65"/>
-      <c r="D20" s="66"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="70"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-    </row>
-    <row r="21" ht="14" customHeight="1">
-      <c r="A21" s="10"/>
-      <c r="B21" s="36" cm="1">
+      <c r="C20" s="46"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+    </row>
+    <row r="21" spans="1:10" ht="14.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="9"/>
+      <c r="B21" s="25" cm="1">
         <f t="array" ref="B21">B20+1</f>
         <v>12</v>
       </c>
-      <c r="C21" s="65"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="70"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-    </row>
-    <row r="22" ht="14" customHeight="1">
-      <c r="A22" s="10"/>
-      <c r="B22" s="36" cm="1">
+      <c r="C21" s="46"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+    </row>
+    <row r="22" spans="1:10" ht="14.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="9"/>
+      <c r="B22" s="25" cm="1">
         <f t="array" ref="B22">B21+1</f>
         <v>13</v>
       </c>
-      <c r="C22" s="65"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="70"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-    </row>
-    <row r="23" ht="13.55" customHeight="1">
-      <c r="A23" s="10"/>
-      <c r="B23" s="36" cm="1">
+      <c r="C22" s="46"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+    </row>
+    <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="9"/>
+      <c r="B23" s="25" cm="1">
         <f t="array" ref="B23">B22+1</f>
         <v>14</v>
       </c>
-      <c r="C23" s="65"/>
-      <c r="D23" s="66"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-    </row>
-    <row r="24" ht="13.55" customHeight="1">
-      <c r="A24" s="10"/>
-      <c r="B24" s="36" cm="1">
+      <c r="C23" s="46"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+    </row>
+    <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="9"/>
+      <c r="B24" s="25" cm="1">
         <f t="array" ref="B24">B23+1</f>
         <v>15</v>
       </c>
-      <c r="C24" s="65"/>
-      <c r="D24" s="66"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="66"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-    </row>
-    <row r="25" ht="13.55" customHeight="1">
-      <c r="A25" s="10"/>
-      <c r="B25" s="36" cm="1">
+      <c r="C24" s="46"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+    </row>
+    <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="9"/>
+      <c r="B25" s="25" cm="1">
         <f t="array" ref="B25">B24+1</f>
         <v>16</v>
       </c>
-      <c r="C25" s="65"/>
-      <c r="D25" s="66"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="66"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-    </row>
-    <row r="26" ht="13.55" customHeight="1">
-      <c r="A26" s="10"/>
-      <c r="B26" s="36" cm="1">
+      <c r="C25" s="46"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+    </row>
+    <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="9"/>
+      <c r="B26" s="25" cm="1">
         <f t="array" ref="B26">B25+1</f>
         <v>17</v>
       </c>
-      <c r="C26" s="65"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="66"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-    </row>
-    <row r="27" ht="13.55" customHeight="1">
-      <c r="A27" s="10"/>
-      <c r="B27" s="36" cm="1">
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+    </row>
+    <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="9"/>
+      <c r="B27" s="25" cm="1">
         <f t="array" ref="B27">B26+1</f>
         <v>18</v>
       </c>
-      <c r="C27" s="39"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-    </row>
-    <row r="28" ht="13.55" customHeight="1">
-      <c r="A28" s="10"/>
-      <c r="B28" s="36" cm="1">
+      <c r="C27" s="28"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+    </row>
+    <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="9"/>
+      <c r="B28" s="25" cm="1">
         <f t="array" ref="B28">B27+1</f>
         <v>19</v>
       </c>
-      <c r="C28" s="39"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-    </row>
-    <row r="29" ht="13.55" customHeight="1">
-      <c r="A29" s="10"/>
-      <c r="B29" s="36" cm="1">
+      <c r="C28" s="28"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+    </row>
+    <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="9"/>
+      <c r="B29" s="25" cm="1">
         <f t="array" ref="B29">B28+1</f>
         <v>20</v>
       </c>
-      <c r="C29" s="39"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-    </row>
-    <row r="30" ht="13.55" customHeight="1">
-      <c r="A30" s="10"/>
-      <c r="B30" s="36" cm="1">
+      <c r="C29" s="28"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+    </row>
+    <row r="30" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="9"/>
+      <c r="B30" s="25" cm="1">
         <f t="array" ref="B30">B29+1</f>
         <v>21</v>
       </c>
-      <c r="C30" s="39"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="51"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-    </row>
-    <row r="31" ht="13.55" customHeight="1">
-      <c r="A31" s="9"/>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-    </row>
-    <row r="32" ht="13.55" customHeight="1">
-      <c r="A32" s="9"/>
-      <c r="B32" s="10"/>
-      <c r="C32" t="s" s="71">
+      <c r="C30" s="28"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+    </row>
+    <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="8"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+    </row>
+    <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="8"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="74" t="s">
         <v>129</v>
       </c>
-      <c r="D32" s="72"/>
-      <c r="E32" s="72"/>
-      <c r="F32" t="s" s="73">
+      <c r="D32" s="75"/>
+      <c r="E32" s="75"/>
+      <c r="F32" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-    </row>
-    <row r="33" ht="13.55" customHeight="1">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-    </row>
-    <row r="34" ht="13.55" customHeight="1">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-    </row>
-    <row r="35" ht="13.55" customHeight="1">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+    </row>
+    <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+    </row>
+    <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+    </row>
+    <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4357,7 +4388,7 @@
     <mergeCell ref="D6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
